--- a/research/traditional_assets/database/data/netherlands/netherlands_advertising.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_advertising.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.283</v>
+        <v>-0.343</v>
       </c>
       <c r="G2">
-        <v>-0.1996204933586338</v>
+        <v>-0.2724324324324324</v>
       </c>
       <c r="H2">
-        <v>-0.2011385199240987</v>
+        <v>-0.272972972972973</v>
       </c>
       <c r="I2">
-        <v>-0.222011385199241</v>
+        <v>-0.2918918918918919</v>
       </c>
       <c r="J2">
-        <v>-0.222011385199241</v>
+        <v>-0.2918918918918919</v>
       </c>
       <c r="K2">
-        <v>-4.68</v>
+        <v>-2.18</v>
       </c>
       <c r="L2">
-        <v>-0.888045540796964</v>
+        <v>-0.5891891891891892</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>0.1503184713375796</v>
+        <v>0.1387387387387387</v>
       </c>
       <c r="W2">
-        <v>-2.629213483146067</v>
+        <v>-0.5532994923857868</v>
       </c>
       <c r="X2">
-        <v>0.06623037452882902</v>
+        <v>0.1124682564883259</v>
       </c>
       <c r="Y2">
-        <v>-2.695443857674896</v>
+        <v>-0.6657677488741127</v>
       </c>
       <c r="Z2">
-        <v>1.294522230410219</v>
+        <v>1.149068322981367</v>
       </c>
       <c r="AA2">
-        <v>-0.2873986735445836</v>
+        <v>-0.3354037267080746</v>
       </c>
       <c r="AB2">
-        <v>0.06216608935959878</v>
+        <v>0.1075985482645808</v>
       </c>
       <c r="AC2">
-        <v>-0.3495647629041824</v>
+        <v>-0.4430022749726553</v>
       </c>
       <c r="AD2">
-        <v>1.64</v>
+        <v>0.845</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.64</v>
+        <v>0.845</v>
       </c>
       <c r="AG2">
-        <v>-0.72</v>
+        <v>-0.6950000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.09457900807381776</v>
+        <v>0.07074089577228966</v>
       </c>
       <c r="AI2">
-        <v>0.2939068100358423</v>
+        <v>0.2068543451652387</v>
       </c>
       <c r="AJ2">
-        <v>-0.04806408544726302</v>
+        <v>-0.0667948101874099</v>
       </c>
       <c r="AK2">
-        <v>-0.2236024844720497</v>
+        <v>-0.2730844793713164</v>
       </c>
       <c r="AL2">
-        <v>0.341</v>
+        <v>0.126</v>
       </c>
       <c r="AM2">
-        <v>0.328</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AN2">
-        <v>-1.547169811320755</v>
+        <v>-0.8366336633663366</v>
       </c>
       <c r="AO2">
-        <v>-3.431085043988269</v>
+        <v>-8.571428571428571</v>
       </c>
       <c r="AP2">
-        <v>0.6792452830188679</v>
+        <v>0.6881188118811882</v>
       </c>
       <c r="AQ2">
-        <v>-3.567073170731707</v>
+        <v>-12.27272727272727</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Crowd Media Holdings Limited (ASX:CM8)</t>
+          <t>Unith Ltd (ASX:UNT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.283</v>
+        <v>-0.343</v>
       </c>
       <c r="G3">
-        <v>-0.1996204933586338</v>
+        <v>-0.2724324324324324</v>
       </c>
       <c r="H3">
-        <v>-0.2011385199240987</v>
+        <v>-0.272972972972973</v>
       </c>
       <c r="I3">
-        <v>-0.222011385199241</v>
+        <v>-0.2918918918918919</v>
       </c>
       <c r="J3">
-        <v>-0.222011385199241</v>
+        <v>-0.2918918918918919</v>
       </c>
       <c r="K3">
-        <v>-4.68</v>
+        <v>-2.18</v>
       </c>
       <c r="L3">
-        <v>-0.888045540796964</v>
+        <v>-0.5891891891891892</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="V3">
-        <v>0.1503184713375796</v>
+        <v>0.1387387387387387</v>
       </c>
       <c r="W3">
-        <v>-2.629213483146067</v>
+        <v>-0.5532994923857868</v>
       </c>
       <c r="X3">
-        <v>0.06623037452882902</v>
+        <v>0.1124682564883259</v>
       </c>
       <c r="Y3">
-        <v>-2.695443857674896</v>
+        <v>-0.6657677488741127</v>
       </c>
       <c r="Z3">
-        <v>1.294522230410219</v>
+        <v>1.149068322981367</v>
       </c>
       <c r="AA3">
-        <v>-0.2873986735445836</v>
+        <v>-0.3354037267080746</v>
       </c>
       <c r="AB3">
-        <v>0.06216608935959878</v>
+        <v>0.1075985482645808</v>
       </c>
       <c r="AC3">
-        <v>-0.3495647629041824</v>
+        <v>-0.4430022749726553</v>
       </c>
       <c r="AD3">
-        <v>1.64</v>
+        <v>0.845</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.64</v>
+        <v>0.845</v>
       </c>
       <c r="AG3">
-        <v>-0.72</v>
+        <v>-0.6950000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.09457900807381776</v>
+        <v>0.07074089577228966</v>
       </c>
       <c r="AI3">
-        <v>0.2939068100358423</v>
+        <v>0.2068543451652387</v>
       </c>
       <c r="AJ3">
-        <v>-0.04806408544726302</v>
+        <v>-0.0667948101874099</v>
       </c>
       <c r="AK3">
-        <v>-0.2236024844720497</v>
+        <v>-0.2730844793713164</v>
       </c>
       <c r="AL3">
-        <v>0.341</v>
+        <v>0.126</v>
       </c>
       <c r="AM3">
-        <v>0.328</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AN3">
-        <v>-1.547169811320755</v>
+        <v>-0.8366336633663366</v>
       </c>
       <c r="AO3">
-        <v>-3.431085043988269</v>
+        <v>-8.571428571428571</v>
       </c>
       <c r="AP3">
-        <v>0.6792452830188679</v>
+        <v>0.6881188118811882</v>
       </c>
       <c r="AQ3">
-        <v>-3.567073170731707</v>
+        <v>-12.27272727272727</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_advertising.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_advertising.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.343</v>
+        <v>-0.364</v>
       </c>
       <c r="G2">
-        <v>-0.2724324324324324</v>
+        <v>-0.8432835820895521</v>
       </c>
       <c r="H2">
-        <v>-0.272972972972973</v>
+        <v>-0.8432835820895521</v>
       </c>
       <c r="I2">
-        <v>-0.2918918918918919</v>
+        <v>-0.8544776119402985</v>
       </c>
       <c r="J2">
-        <v>-0.2918918918918919</v>
+        <v>-0.8544776119402985</v>
       </c>
       <c r="K2">
-        <v>-2.18</v>
+        <v>-0.487</v>
       </c>
       <c r="L2">
-        <v>-0.5891891891891892</v>
+        <v>-0.1817164179104477</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.54</v>
+        <v>2.84</v>
       </c>
       <c r="V2">
-        <v>0.1387387387387387</v>
+        <v>0.2201550387596899</v>
       </c>
       <c r="W2">
-        <v>-0.5532994923857868</v>
+        <v>-0.1503086419753086</v>
       </c>
       <c r="X2">
-        <v>0.1124682564883259</v>
+        <v>0.09694499821326183</v>
       </c>
       <c r="Y2">
-        <v>-0.6657677488741127</v>
+        <v>-0.2472536401885705</v>
       </c>
       <c r="Z2">
-        <v>1.149068322981367</v>
+        <v>1.053045186640472</v>
       </c>
       <c r="AA2">
-        <v>-0.3354037267080746</v>
+        <v>-0.899803536345776</v>
       </c>
       <c r="AB2">
-        <v>0.1075985482645808</v>
+        <v>0.09412735618330466</v>
       </c>
       <c r="AC2">
-        <v>-0.4430022749726553</v>
+        <v>-0.9939308925290807</v>
       </c>
       <c r="AD2">
-        <v>0.845</v>
+        <v>0.668</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.845</v>
+        <v>0.668</v>
       </c>
       <c r="AG2">
-        <v>-0.6950000000000001</v>
+        <v>-2.172</v>
       </c>
       <c r="AH2">
-        <v>0.07074089577228966</v>
+        <v>0.04923349056603774</v>
       </c>
       <c r="AI2">
-        <v>0.2068543451652387</v>
+        <v>0.09726266744321491</v>
       </c>
       <c r="AJ2">
-        <v>-0.0667948101874099</v>
+        <v>-0.2024608501118568</v>
       </c>
       <c r="AK2">
-        <v>-0.2730844793713164</v>
+        <v>-0.5392254220456801</v>
       </c>
       <c r="AL2">
-        <v>0.126</v>
+        <v>0.051</v>
       </c>
       <c r="AM2">
-        <v>0.08799999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="AN2">
-        <v>-0.8366336633663366</v>
+        <v>-0.2955752212389381</v>
       </c>
       <c r="AO2">
-        <v>-8.571428571428571</v>
+        <v>-44.90196078431373</v>
       </c>
       <c r="AP2">
-        <v>0.6881188118811882</v>
+        <v>0.9610619469026548</v>
       </c>
       <c r="AQ2">
-        <v>-12.27272727272727</v>
+        <v>-71.5625</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.343</v>
+        <v>-0.364</v>
       </c>
       <c r="G3">
-        <v>-0.2724324324324324</v>
+        <v>-0.8432835820895521</v>
       </c>
       <c r="H3">
-        <v>-0.272972972972973</v>
+        <v>-0.8432835820895521</v>
       </c>
       <c r="I3">
-        <v>-0.2918918918918919</v>
+        <v>-0.8544776119402985</v>
       </c>
       <c r="J3">
-        <v>-0.2918918918918919</v>
+        <v>-0.8544776119402985</v>
       </c>
       <c r="K3">
-        <v>-2.18</v>
+        <v>-0.487</v>
       </c>
       <c r="L3">
-        <v>-0.5891891891891892</v>
+        <v>-0.1817164179104477</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.54</v>
+        <v>2.84</v>
       </c>
       <c r="V3">
-        <v>0.1387387387387387</v>
+        <v>0.2201550387596899</v>
       </c>
       <c r="W3">
-        <v>-0.5532994923857868</v>
+        <v>-0.1503086419753086</v>
       </c>
       <c r="X3">
-        <v>0.1124682564883259</v>
+        <v>0.09694499821326183</v>
       </c>
       <c r="Y3">
-        <v>-0.6657677488741127</v>
+        <v>-0.2472536401885705</v>
       </c>
       <c r="Z3">
-        <v>1.149068322981367</v>
+        <v>1.053045186640472</v>
       </c>
       <c r="AA3">
-        <v>-0.3354037267080746</v>
+        <v>-0.899803536345776</v>
       </c>
       <c r="AB3">
-        <v>0.1075985482645808</v>
+        <v>0.09412735618330466</v>
       </c>
       <c r="AC3">
-        <v>-0.4430022749726553</v>
+        <v>-0.9939308925290807</v>
       </c>
       <c r="AD3">
-        <v>0.845</v>
+        <v>0.668</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.845</v>
+        <v>0.668</v>
       </c>
       <c r="AG3">
-        <v>-0.6950000000000001</v>
+        <v>-2.172</v>
       </c>
       <c r="AH3">
-        <v>0.07074089577228966</v>
+        <v>0.04923349056603774</v>
       </c>
       <c r="AI3">
-        <v>0.2068543451652387</v>
+        <v>0.09726266744321491</v>
       </c>
       <c r="AJ3">
-        <v>-0.0667948101874099</v>
+        <v>-0.2024608501118568</v>
       </c>
       <c r="AK3">
-        <v>-0.2730844793713164</v>
+        <v>-0.5392254220456801</v>
       </c>
       <c r="AL3">
-        <v>0.126</v>
+        <v>0.051</v>
       </c>
       <c r="AM3">
-        <v>0.08799999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="AN3">
-        <v>-0.8366336633663366</v>
+        <v>-0.2955752212389381</v>
       </c>
       <c r="AO3">
-        <v>-8.571428571428571</v>
+        <v>-44.90196078431373</v>
       </c>
       <c r="AP3">
-        <v>0.6881188118811882</v>
+        <v>0.9610619469026548</v>
       </c>
       <c r="AQ3">
-        <v>-12.27272727272727</v>
+        <v>-71.5625</v>
       </c>
     </row>
   </sheetData>
